--- a/27SS 출고계획 조율/output/27SS_소재일정_역산_트래커_구글시트용.xlsx
+++ b/27SS 출고계획 조율/output/27SS_소재일정_역산_트래커_구글시트용.xlsx
@@ -11,8 +11,9 @@
     <sheet name="기준정보" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="소재역산 트래커" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="소재DB_RAW" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="금액 요약" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="리스크 요약" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EDW_RAW" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="금액 요약" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="리스크 요약" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'소재역산 트래커'!$A$4:$AH$428</definedName>
@@ -767,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B39"/>
+  <dimension ref="B2:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="114" customWidth="1" min="2" max="2"/>
@@ -972,26 +973,33 @@
     <row r="36">
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>· 최초 1회: 시트를 열고 '소재DB_RAW' 탭(숨김 해제)에서 A3 셀의 '액세스 허용' 클릭 필요 — 이후 자동 갱신</t>
+          <t>· 사양확정: '27SS 생산 프로세스 진척현황(자동화)' EDW_RAW와 실시간 연동 (숨김 탭 'EDW_RAW') — 컬러 전체 결재 O / 일부 '부분' / 없음 X</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>· 생산처(소재DB) 열은 크로스체크용 — 0808 생산처와 다르면 빨간색 표시 (픽스처/픽스쳐 같은 표기 차이도 포함되니 확인 필요)</t>
+          <t>· 최초 1회: '소재DB_RAW' 탭 A3 셀과 'EDW_RAW' 탭 A2 셀에서 각각 '액세스 허용' 클릭 필요 — 이후 자동 갱신</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>· WM/피싱(8로 시작)은 0808 원본에 기획수량 0으로 입력되어 수량 합계 공란 — 금액은 원본 총원가/총공급가 기준</t>
+          <t>· 생산처(소재DB) 열은 크로스체크용 — 0808 생산처와 다르면 빨간색 표시 (픽스처/픽스쳐 같은 표기 차이도 포함되니 확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>· WM/피싱(8로 시작)은 0808 원본에 기획수량 0으로 입력되어 수량 합계 공란 — 금액은 원본 총원가/총공급가 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>· 8UTCM27101은 컬러별 출고일 상이(1월3주/4월2주) → 다수 값 적용, 확인 필요</t>
         </is>
@@ -1345,7 +1353,7 @@
       </c>
       <c r="R4" s="18" t="inlineStr">
         <is>
-          <t>사양확정 (전산 8/6)</t>
+          <t>사양확정 (전산 실시간)</t>
         </is>
       </c>
       <c r="S4" s="18" t="inlineStr">
@@ -1503,10 +1511,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R5" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D5)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D5,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D5),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D5,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S5" s="25" t="n"/>
       <c r="T5" s="20">
@@ -1634,10 +1641,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R6" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D6)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D6,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D6),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D6,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S6" s="25" t="n"/>
       <c r="T6" s="20">
@@ -1765,10 +1771,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R7" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D7)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D7,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D7),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D7,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S7" s="25" t="n"/>
       <c r="T7" s="20">
@@ -1896,10 +1901,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R8" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D8)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D8,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D8),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D8,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S8" s="25" t="n"/>
       <c r="T8" s="20">
@@ -2027,10 +2031,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R9" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D9)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D9,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D9),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D9,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S9" s="25" t="n"/>
       <c r="T9" s="20">
@@ -2158,10 +2161,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R10" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D10)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D10,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D10),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D10,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S10" s="25" t="n"/>
       <c r="T10" s="20">
@@ -2289,10 +2291,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R11" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R11" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D11)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D11,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D11),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D11,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S11" s="25" t="n"/>
       <c r="T11" s="20">
@@ -2420,10 +2421,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R12" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D12)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D12,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D12),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D12,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S12" s="25" t="n"/>
       <c r="T12" s="20">
@@ -2551,10 +2551,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R13" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R13" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D13)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D13,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D13),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D13,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S13" s="25" t="n"/>
       <c r="T13" s="20">
@@ -2682,10 +2681,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R14" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D14)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D14,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D14),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D14,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S14" s="25" t="n"/>
       <c r="T14" s="20">
@@ -2813,10 +2811,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R15" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R15" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D15)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D15,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D15),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D15,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S15" s="25" t="n"/>
       <c r="T15" s="20">
@@ -2944,10 +2941,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R16" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R16" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D16)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D16,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D16),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D16,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S16" s="25" t="n"/>
       <c r="T16" s="20">
@@ -3075,10 +3071,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R17" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R17" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D17)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D17,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D17),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D17,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S17" s="25" t="n"/>
       <c r="T17" s="20">
@@ -3206,10 +3201,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R18" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R18" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D18)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D18,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D18),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D18,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S18" s="25" t="n"/>
       <c r="T18" s="20">
@@ -3333,10 +3327,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R19" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R19" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D19)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D19,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D19),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D19,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S19" s="25" t="n"/>
       <c r="T19" s="20">
@@ -3460,10 +3453,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R20" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D20)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D20,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D20),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D20,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S20" s="25" t="n"/>
       <c r="T20" s="20">
@@ -3591,10 +3583,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R21" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R21" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D21)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D21,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D21),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D21,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S21" s="25" t="n"/>
       <c r="T21" s="20">
@@ -3718,10 +3709,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R22" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D22)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D22,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D22),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D22,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S22" s="25" t="n"/>
       <c r="T22" s="20">
@@ -3853,10 +3843,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R23" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R23" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D23)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D23,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D23),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D23,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S23" s="25" t="n"/>
       <c r="T23" s="20">
@@ -3984,10 +3973,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R24" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R24" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D24)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D24,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D24),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D24,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S24" s="25" t="n"/>
       <c r="T24" s="20">
@@ -4115,10 +4103,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R25" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R25" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D25)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D25,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D25),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D25,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S25" s="25" t="n"/>
       <c r="T25" s="20">
@@ -4246,10 +4233,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R26" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R26" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D26)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D26,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D26),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D26,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S26" s="25" t="n"/>
       <c r="T26" s="20">
@@ -4377,10 +4363,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R27" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R27" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D27)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D27,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D27),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D27,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S27" s="25" t="n"/>
       <c r="T27" s="20">
@@ -4508,10 +4493,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R28" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D28)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D28,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D28),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D28,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S28" s="25" t="n"/>
       <c r="T28" s="20">
@@ -4639,10 +4623,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R29" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R29" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D29)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D29,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D29),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D29,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S29" s="25" t="n"/>
       <c r="T29" s="20">
@@ -4770,10 +4753,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R30" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R30" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D30)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D30,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D30),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D30,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S30" s="25" t="n"/>
       <c r="T30" s="20">
@@ -4901,10 +4883,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R31" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R31" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D31)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D31,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D31),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D31,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S31" s="25" t="n"/>
       <c r="T31" s="20">
@@ -5032,10 +5013,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R32" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R32" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D32)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D32,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D32),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D32,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S32" s="25" t="n"/>
       <c r="T32" s="20">
@@ -5163,7 +5143,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R33" s="21" t="n"/>
+      <c r="R33" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D33)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D33,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D33),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D33,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S33" s="25" t="n"/>
       <c r="T33" s="20">
         <f>IF($H33="","",IF(AND(ISNUMBER(SEARCH("CMT",$H33)),OR(ISNUMBER(SEARCH("완사입",$H33)),ISNUMBER(SEARCH("ODM",$H33)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H33)),"본사(소재팀)","생산처")))</f>
@@ -5290,10 +5273,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R34" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R34" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D34)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D34,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D34),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D34,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S34" s="25" t="n"/>
       <c r="T34" s="20">
@@ -5421,10 +5403,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R35" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R35" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D35)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D35,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D35),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D35,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S35" s="25" t="n"/>
       <c r="T35" s="20">
@@ -5552,7 +5533,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R36" s="21" t="n"/>
+      <c r="R36" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D36)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D36,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D36),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D36,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S36" s="25" t="n"/>
       <c r="T36" s="20">
         <f>IF($H36="","",IF(AND(ISNUMBER(SEARCH("CMT",$H36)),OR(ISNUMBER(SEARCH("완사입",$H36)),ISNUMBER(SEARCH("ODM",$H36)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H36)),"본사(소재팀)","생산처")))</f>
@@ -5679,10 +5663,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R37" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R37" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D37)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D37,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D37),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D37,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S37" s="25" t="n"/>
       <c r="T37" s="20">
@@ -5810,10 +5793,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R38" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R38" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D38)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D38,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D38),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D38,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S38" s="25" t="n"/>
       <c r="T38" s="20">
@@ -5941,10 +5923,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R39" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R39" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D39)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D39,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D39),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D39,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S39" s="25" t="n"/>
       <c r="T39" s="20">
@@ -6068,10 +6049,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R40" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R40" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D40)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D40,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D40),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D40,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S40" s="25" t="n"/>
       <c r="T40" s="20">
@@ -6195,10 +6175,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R41" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R41" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D41)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D41,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D41),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D41,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S41" s="25" t="n"/>
       <c r="T41" s="20">
@@ -6326,10 +6305,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R42" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R42" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D42)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D42,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D42),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D42,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S42" s="25" t="n"/>
       <c r="T42" s="20">
@@ -6457,10 +6435,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R43" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R43" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D43)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D43,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D43),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D43,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S43" s="25" t="n"/>
       <c r="T43" s="20">
@@ -6588,10 +6565,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R44" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R44" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D44)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D44,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D44),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D44,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S44" s="25" t="n"/>
       <c r="T44" s="20">
@@ -6715,10 +6691,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R45" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R45" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D45)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D45,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D45),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D45,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S45" s="25" t="n"/>
       <c r="T45" s="20">
@@ -6846,10 +6821,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R46" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R46" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D46)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D46,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D46),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D46,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S46" s="25" t="n"/>
       <c r="T46" s="20">
@@ -6977,10 +6951,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R47" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R47" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D47)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D47,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D47),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D47,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S47" s="25" t="n"/>
       <c r="T47" s="20">
@@ -7108,10 +7081,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R48" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R48" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D48)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D48,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D48),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D48,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S48" s="25" t="n"/>
       <c r="T48" s="20">
@@ -7243,10 +7215,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R49" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R49" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D49)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D49,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D49),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D49,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S49" s="25" t="n"/>
       <c r="T49" s="20">
@@ -7370,10 +7341,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R50" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R50" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D50)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D50,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D50),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D50,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S50" s="25" t="n"/>
       <c r="T50" s="20">
@@ -7497,10 +7467,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R51" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R51" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D51)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D51,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D51),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D51,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S51" s="25" t="n"/>
       <c r="T51" s="20">
@@ -7624,10 +7593,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R52" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R52" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D52)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D52,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D52),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D52,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S52" s="25" t="n"/>
       <c r="T52" s="20">
@@ -7751,10 +7719,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R53" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R53" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D53)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D53,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D53),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D53,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S53" s="25" t="n"/>
       <c r="T53" s="20">
@@ -7878,10 +7845,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R54" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R54" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D54)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D54,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D54),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D54,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S54" s="25" t="n"/>
       <c r="T54" s="20">
@@ -8009,10 +7975,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R55" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R55" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D55)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D55,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D55),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D55,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S55" s="25" t="n"/>
       <c r="T55" s="20">
@@ -8140,10 +8105,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R56" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R56" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D56)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D56,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D56),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D56,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S56" s="25" t="n"/>
       <c r="T56" s="20">
@@ -8271,10 +8235,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R57" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R57" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D57)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D57,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D57),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D57,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S57" s="25" t="n"/>
       <c r="T57" s="20">
@@ -8402,10 +8365,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R58" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R58" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D58)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D58,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D58),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D58,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S58" s="25" t="n"/>
       <c r="T58" s="20">
@@ -8533,10 +8495,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R59" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R59" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D59)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D59,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D59),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D59,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S59" s="25" t="n"/>
       <c r="T59" s="20">
@@ -8660,7 +8621,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R60" s="21" t="n"/>
+      <c r="R60" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D60)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D60,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D60),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D60,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S60" s="25" t="n"/>
       <c r="T60" s="20">
         <f>IF($H60="","",IF(AND(ISNUMBER(SEARCH("CMT",$H60)),OR(ISNUMBER(SEARCH("완사입",$H60)),ISNUMBER(SEARCH("ODM",$H60)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H60)),"본사(소재팀)","생산처")))</f>
@@ -8787,10 +8751,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R61" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R61" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D61)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D61,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D61),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D61,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S61" s="25" t="n"/>
       <c r="T61" s="20">
@@ -8918,10 +8881,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R62" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R62" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D62)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D62,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D62),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D62,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S62" s="25" t="n"/>
       <c r="T62" s="20">
@@ -9049,10 +9011,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R63" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R63" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D63)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D63,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D63),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D63,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S63" s="25" t="n"/>
       <c r="T63" s="20">
@@ -9180,10 +9141,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R64" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R64" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D64)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D64,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D64),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D64,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S64" s="25" t="n"/>
       <c r="T64" s="20">
@@ -9307,10 +9267,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R65" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R65" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D65)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D65,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D65),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D65,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S65" s="25" t="n"/>
       <c r="T65" s="20">
@@ -9438,10 +9397,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R66" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R66" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D66)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D66,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D66),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D66,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S66" s="25" t="n"/>
       <c r="T66" s="20">
@@ -9569,10 +9527,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R67" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R67" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D67)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D67,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D67),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D67,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S67" s="25" t="n"/>
       <c r="T67" s="20">
@@ -9700,10 +9657,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R68" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R68" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D68)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D68,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D68),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D68,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S68" s="25" t="n"/>
       <c r="T68" s="20">
@@ -9831,10 +9787,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R69" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R69" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D69)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D69,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D69),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D69,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S69" s="25" t="n"/>
       <c r="T69" s="20">
@@ -9966,10 +9921,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R70" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R70" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D70)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D70,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D70),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D70,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S70" s="25" t="n"/>
       <c r="T70" s="20">
@@ -10097,10 +10051,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R71" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R71" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D71)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D71,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D71),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D71,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S71" s="25" t="n"/>
       <c r="T71" s="20">
@@ -10228,10 +10181,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R72" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R72" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D72)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D72,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D72),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D72,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S72" s="25" t="n"/>
       <c r="T72" s="20">
@@ -10359,10 +10311,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R73" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R73" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D73)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D73,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D73),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D73,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S73" s="25" t="n"/>
       <c r="T73" s="20">
@@ -10486,10 +10437,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R74" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R74" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D74)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D74,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D74),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D74,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S74" s="25" t="n"/>
       <c r="T74" s="20">
@@ -10613,10 +10563,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R75" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R75" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D75)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D75,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D75),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D75,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S75" s="25" t="n"/>
       <c r="T75" s="20">
@@ -10744,10 +10693,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R76" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R76" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D76)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D76,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D76),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D76,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S76" s="25" t="n"/>
       <c r="T76" s="20">
@@ -10875,10 +10823,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R77" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R77" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D77)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D77,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D77),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D77,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S77" s="25" t="n"/>
       <c r="T77" s="20">
@@ -11006,10 +10953,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R78" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R78" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D78)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D78,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D78),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D78,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S78" s="25" t="n"/>
       <c r="T78" s="20">
@@ -11137,10 +11083,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R79" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R79" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D79)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D79,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D79),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D79,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S79" s="25" t="n"/>
       <c r="T79" s="20">
@@ -11264,10 +11209,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R80" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R80" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D80)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D80,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D80),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D80,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S80" s="25" t="n"/>
       <c r="T80" s="20">
@@ -11395,10 +11339,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R81" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R81" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D81)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D81,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D81),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D81,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S81" s="25" t="n"/>
       <c r="T81" s="20">
@@ -11522,10 +11465,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R82" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R82" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D82)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D82,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D82),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D82,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S82" s="25" t="n"/>
       <c r="T82" s="20">
@@ -11653,10 +11595,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R83" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R83" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D83)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D83,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D83),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D83,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S83" s="25" t="n"/>
       <c r="T83" s="20">
@@ -11784,10 +11725,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R84" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R84" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D84)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D84,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D84),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D84,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S84" s="25" t="n"/>
       <c r="T84" s="20">
@@ -11915,10 +11855,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R85" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R85" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D85)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D85,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D85),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D85,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S85" s="25" t="n"/>
       <c r="T85" s="20">
@@ -12050,10 +11989,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R86" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R86" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D86)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D86,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D86),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D86,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S86" s="25" t="n"/>
       <c r="T86" s="20">
@@ -12181,10 +12119,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R87" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R87" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D87)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D87,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D87),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D87,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S87" s="25" t="n"/>
       <c r="T87" s="20">
@@ -12316,10 +12253,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R88" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R88" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D88)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D88,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D88),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D88,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S88" s="25" t="n"/>
       <c r="T88" s="20">
@@ -12447,10 +12383,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R89" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R89" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D89)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D89,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D89),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D89,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S89" s="25" t="n"/>
       <c r="T89" s="20">
@@ -12574,10 +12509,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R90" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R90" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D90)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D90,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D90),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D90,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S90" s="25" t="n"/>
       <c r="T90" s="20">
@@ -12705,10 +12639,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R91" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R91" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D91)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D91,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D91),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D91,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S91" s="25" t="n"/>
       <c r="T91" s="20">
@@ -12832,10 +12765,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R92" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R92" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D92)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D92,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D92),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D92,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S92" s="25" t="n"/>
       <c r="T92" s="20">
@@ -12963,10 +12895,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R93" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R93" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D93)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D93,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D93),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D93,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S93" s="25" t="n"/>
       <c r="T93" s="20">
@@ -13090,10 +13021,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R94" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R94" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D94)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D94,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D94),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D94,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S94" s="25" t="n"/>
       <c r="T94" s="20">
@@ -13217,10 +13147,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R95" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R95" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D95)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D95,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D95),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D95,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S95" s="25" t="n"/>
       <c r="T95" s="20">
@@ -13344,10 +13273,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R96" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R96" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D96)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D96,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D96),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D96,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S96" s="25" t="n"/>
       <c r="T96" s="20">
@@ -13475,10 +13403,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R97" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R97" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D97)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D97,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D97),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D97,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S97" s="25" t="n"/>
       <c r="T97" s="20">
@@ -13606,10 +13533,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R98" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R98" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D98)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D98,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D98),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D98,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S98" s="25" t="n"/>
       <c r="T98" s="20">
@@ -13737,10 +13663,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R99" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R99" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D99)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D99,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D99),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D99,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S99" s="25" t="n"/>
       <c r="T99" s="20">
@@ -13868,10 +13793,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R100" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R100" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D100)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D100,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D100),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D100,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S100" s="25" t="n"/>
       <c r="T100" s="20">
@@ -13995,10 +13919,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R101" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R101" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D101)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D101,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D101),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D101,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S101" s="25" t="n"/>
       <c r="T101" s="20">
@@ -14130,10 +14053,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R102" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R102" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D102)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D102,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D102),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D102,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S102" s="25" t="n"/>
       <c r="T102" s="20">
@@ -14265,10 +14187,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R103" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R103" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D103)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D103,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D103),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D103,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S103" s="25" t="n"/>
       <c r="T103" s="20">
@@ -14392,10 +14313,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R104" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R104" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D104)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D104,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D104),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D104,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S104" s="25" t="n"/>
       <c r="T104" s="20">
@@ -14515,10 +14435,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R105" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R105" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D105)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D105,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D105),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D105,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S105" s="25" t="n"/>
       <c r="T105" s="20">
@@ -14638,10 +14557,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R106" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R106" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D106)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D106,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D106),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D106,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S106" s="25" t="n"/>
       <c r="T106" s="20">
@@ -14765,10 +14683,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R107" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R107" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D107)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D107,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D107),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D107,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S107" s="25" t="n"/>
       <c r="T107" s="20">
@@ -14896,10 +14813,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R108" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R108" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D108)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D108,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D108),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D108,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S108" s="25" t="n"/>
       <c r="T108" s="20">
@@ -15027,10 +14943,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R109" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R109" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D109)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D109,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D109),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D109,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S109" s="25" t="n"/>
       <c r="T109" s="20">
@@ -15158,10 +15073,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R110" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R110" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D110)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D110,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D110),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D110,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S110" s="25" t="n"/>
       <c r="T110" s="20">
@@ -15289,10 +15203,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R111" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R111" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D111)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D111,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D111),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D111,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S111" s="25" t="n"/>
       <c r="T111" s="20">
@@ -15420,10 +15333,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R112" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R112" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D112)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D112,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D112),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D112,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S112" s="25" t="n"/>
       <c r="T112" s="20">
@@ -15551,10 +15463,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R113" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R113" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D113)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D113,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D113),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D113,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S113" s="25" t="n"/>
       <c r="T113" s="20">
@@ -15686,10 +15597,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R114" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R114" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D114)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D114,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D114),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D114,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S114" s="25" t="n"/>
       <c r="T114" s="20">
@@ -15821,10 +15731,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R115" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R115" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D115)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D115,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D115),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D115,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S115" s="25" t="n"/>
       <c r="T115" s="20">
@@ -15956,10 +15865,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R116" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R116" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D116)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D116,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D116),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D116,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S116" s="25" t="n"/>
       <c r="T116" s="20">
@@ -16095,10 +16003,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R117" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R117" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D117)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D117,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D117),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D117,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S117" s="25" t="n"/>
       <c r="T117" s="20">
@@ -16226,10 +16133,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R118" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R118" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D118)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D118,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D118),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D118,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S118" s="25" t="n"/>
       <c r="T118" s="20">
@@ -16361,10 +16267,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R119" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R119" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D119)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D119,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D119),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D119,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S119" s="25" t="n"/>
       <c r="T119" s="20">
@@ -16492,10 +16397,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R120" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R120" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D120)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D120,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D120),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D120,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S120" s="25" t="n"/>
       <c r="T120" s="20">
@@ -16623,10 +16527,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R121" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R121" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D121)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D121,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D121),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D121,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S121" s="25" t="n"/>
       <c r="T121" s="20">
@@ -16754,10 +16657,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R122" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R122" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D122)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D122,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D122),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D122,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S122" s="25" t="n"/>
       <c r="T122" s="20">
@@ -16885,10 +16787,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R123" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R123" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D123)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D123,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D123),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D123,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S123" s="25" t="n"/>
       <c r="T123" s="20">
@@ -17020,10 +16921,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R124" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R124" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D124)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D124,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D124),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D124,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S124" s="25" t="n"/>
       <c r="T124" s="20">
@@ -17151,10 +17051,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R125" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R125" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D125)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D125,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D125),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D125,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S125" s="25" t="n"/>
       <c r="T125" s="20">
@@ -17286,10 +17185,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R126" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R126" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D126)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D126,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D126),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D126,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S126" s="25" t="n"/>
       <c r="T126" s="20">
@@ -17421,10 +17319,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R127" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R127" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D127)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D127,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D127),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D127,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S127" s="25" t="n"/>
       <c r="T127" s="20">
@@ -17552,10 +17449,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R128" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R128" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D128)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D128,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D128),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D128,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S128" s="25" t="n"/>
       <c r="T128" s="20">
@@ -17687,10 +17583,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R129" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R129" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D129)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D129,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D129),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D129,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S129" s="25" t="n"/>
       <c r="T129" s="20">
@@ -17822,10 +17717,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R130" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R130" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D130)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D130,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D130),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D130,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S130" s="25" t="n"/>
       <c r="T130" s="20">
@@ -17957,10 +17851,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R131" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R131" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D131)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D131,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D131),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D131,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S131" s="25" t="n"/>
       <c r="T131" s="20">
@@ -18092,10 +17985,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R132" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R132" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D132)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D132,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D132),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D132,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S132" s="25" t="n"/>
       <c r="T132" s="20">
@@ -18223,10 +18115,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R133" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R133" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D133)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D133,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D133),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D133,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S133" s="25" t="n"/>
       <c r="T133" s="20">
@@ -18358,10 +18249,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R134" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R134" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D134)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D134,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D134),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D134,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S134" s="25" t="n"/>
       <c r="T134" s="20">
@@ -18489,10 +18379,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R135" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R135" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D135)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D135,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D135),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D135,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S135" s="25" t="n"/>
       <c r="T135" s="20">
@@ -18624,10 +18513,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R136" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R136" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D136)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D136,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D136),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D136,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S136" s="25" t="n"/>
       <c r="T136" s="20">
@@ -18755,10 +18643,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R137" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R137" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D137)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D137,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D137),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D137,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S137" s="25" t="n"/>
       <c r="T137" s="20">
@@ -18890,10 +18777,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R138" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R138" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D138)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D138,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D138),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D138,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S138" s="25" t="n"/>
       <c r="T138" s="20">
@@ -19029,10 +18915,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R139" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R139" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D139)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D139,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D139),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D139,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S139" s="25" t="n"/>
       <c r="T139" s="20">
@@ -19160,10 +19045,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R140" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R140" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D140)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D140,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D140),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D140,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S140" s="25" t="n"/>
       <c r="T140" s="20">
@@ -19295,10 +19179,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R141" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R141" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D141)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D141,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D141),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D141,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S141" s="25" t="n"/>
       <c r="T141" s="20">
@@ -19430,10 +19313,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R142" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R142" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D142)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D142,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D142),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D142,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S142" s="25" t="n"/>
       <c r="T142" s="20">
@@ -19565,10 +19447,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R143" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R143" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D143)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D143,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D143),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D143,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S143" s="25" t="n"/>
       <c r="T143" s="20">
@@ -19704,10 +19585,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R144" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R144" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D144)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D144,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D144),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D144,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S144" s="25" t="n"/>
       <c r="T144" s="20">
@@ -19839,10 +19719,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R145" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R145" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D145)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D145,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D145),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D145,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S145" s="25" t="n"/>
       <c r="T145" s="20">
@@ -19974,10 +19853,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R146" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R146" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D146)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D146,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D146),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D146,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S146" s="25" t="n"/>
       <c r="T146" s="20">
@@ -20109,10 +19987,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R147" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R147" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D147)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D147,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D147),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D147,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S147" s="25" t="n"/>
       <c r="T147" s="20">
@@ -20244,10 +20121,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R148" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R148" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D148)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D148,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D148),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D148,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S148" s="25" t="n"/>
       <c r="T148" s="20">
@@ -20379,10 +20255,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R149" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R149" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D149)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D149,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D149),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D149,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S149" s="25" t="n"/>
       <c r="T149" s="20">
@@ -20514,10 +20389,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R150" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R150" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D150)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D150,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D150),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D150,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S150" s="25" t="n"/>
       <c r="T150" s="20">
@@ -20645,10 +20519,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R151" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R151" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D151)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D151,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D151),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D151,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S151" s="25" t="n"/>
       <c r="T151" s="20">
@@ -20780,10 +20653,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R152" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R152" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D152)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D152,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D152),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D152,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S152" s="25" t="n"/>
       <c r="T152" s="20">
@@ -20915,10 +20787,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R153" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R153" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D153)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D153,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D153),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D153,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S153" s="25" t="n"/>
       <c r="T153" s="20">
@@ -21050,10 +20921,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R154" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R154" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D154)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D154,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D154),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D154,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S154" s="25" t="n"/>
       <c r="T154" s="20">
@@ -21185,10 +21055,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R155" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R155" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D155)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D155,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D155),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D155,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S155" s="25" t="n"/>
       <c r="T155" s="20">
@@ -21320,10 +21189,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R156" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R156" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D156)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D156,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D156),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D156,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S156" s="25" t="n"/>
       <c r="T156" s="20">
@@ -21455,10 +21323,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R157" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R157" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D157)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D157,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D157),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D157,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S157" s="25" t="n"/>
       <c r="T157" s="20">
@@ -21590,10 +21457,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R158" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R158" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D158)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D158,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D158),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D158,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S158" s="25" t="n"/>
       <c r="T158" s="20">
@@ -21725,10 +21591,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R159" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R159" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D159)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D159,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D159),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D159,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S159" s="25" t="n"/>
       <c r="T159" s="20">
@@ -21856,10 +21721,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R160" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R160" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D160)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D160,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D160),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D160,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S160" s="25" t="n"/>
       <c r="T160" s="20">
@@ -21987,10 +21851,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R161" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R161" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D161)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D161,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D161),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D161,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S161" s="25" t="n"/>
       <c r="T161" s="20">
@@ -22118,10 +21981,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R162" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R162" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D162)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D162,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D162),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D162,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S162" s="25" t="n"/>
       <c r="T162" s="20">
@@ -22249,10 +22111,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R163" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R163" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D163)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D163,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D163),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D163,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S163" s="25" t="n"/>
       <c r="T163" s="20">
@@ -22376,10 +22237,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R164" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R164" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D164)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D164,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D164),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D164,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S164" s="25" t="n"/>
       <c r="T164" s="20">
@@ -22503,10 +22363,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R165" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R165" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D165)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D165,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D165),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D165,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S165" s="25" t="n"/>
       <c r="T165" s="20">
@@ -22634,10 +22493,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R166" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R166" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D166)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D166,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D166),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D166,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S166" s="25" t="n"/>
       <c r="T166" s="20">
@@ -22765,10 +22623,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R167" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R167" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D167)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D167,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D167),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D167,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S167" s="25" t="n"/>
       <c r="T167" s="20">
@@ -22896,10 +22753,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R168" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R168" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D168)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D168,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D168),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D168,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S168" s="25" t="n"/>
       <c r="T168" s="20">
@@ -23027,10 +22883,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R169" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R169" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D169)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D169,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D169),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D169,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S169" s="25" t="n"/>
       <c r="T169" s="20">
@@ -23158,10 +23013,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R170" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R170" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D170)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D170,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D170),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D170,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S170" s="25" t="n"/>
       <c r="T170" s="20">
@@ -23289,10 +23143,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R171" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R171" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D171)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D171,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D171),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D171,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S171" s="25" t="n"/>
       <c r="T171" s="20">
@@ -23420,10 +23273,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R172" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R172" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D172)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D172,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D172),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D172,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S172" s="25" t="n"/>
       <c r="T172" s="20">
@@ -23555,10 +23407,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R173" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R173" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D173)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D173,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D173),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D173,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S173" s="25" t="n"/>
       <c r="T173" s="20">
@@ -23690,10 +23541,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R174" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R174" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D174)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D174,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D174),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D174,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S174" s="25" t="n"/>
       <c r="T174" s="20">
@@ -23825,10 +23675,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R175" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R175" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D175)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D175,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D175),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D175,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S175" s="25" t="n"/>
       <c r="T175" s="20">
@@ -23956,10 +23805,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R176" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R176" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D176)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D176,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D176),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D176,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S176" s="25" t="n"/>
       <c r="T176" s="20">
@@ -24087,10 +23935,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R177" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R177" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D177)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D177,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D177),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D177,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S177" s="25" t="n"/>
       <c r="T177" s="20">
@@ -24218,10 +24065,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R178" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R178" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D178)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D178,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D178),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D178,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S178" s="25" t="n"/>
       <c r="T178" s="20">
@@ -24345,10 +24191,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R179" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R179" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D179)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D179,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D179),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D179,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S179" s="25" t="n"/>
       <c r="T179" s="20">
@@ -24476,10 +24321,9 @@
           <t>부분</t>
         </is>
       </c>
-      <c r="R180" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R180" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D180)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D180,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D180),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D180,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S180" s="25" t="n"/>
       <c r="T180" s="20">
@@ -24603,10 +24447,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R181" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R181" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D181)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D181,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D181),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D181,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S181" s="25" t="n"/>
       <c r="T181" s="20">
@@ -24734,10 +24577,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R182" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R182" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D182)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D182,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D182),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D182,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S182" s="25" t="n"/>
       <c r="T182" s="20">
@@ -24865,10 +24707,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R183" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R183" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D183)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D183,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D183),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D183,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S183" s="25" t="n"/>
       <c r="T183" s="20">
@@ -25000,10 +24841,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R184" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R184" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D184)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D184,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D184),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D184,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S184" s="25" t="n"/>
       <c r="T184" s="20">
@@ -25127,7 +24967,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R185" s="21" t="n"/>
+      <c r="R185" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D185)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D185,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D185),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D185,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S185" s="25" t="n"/>
       <c r="T185" s="20">
         <f>IF($H185="","",IF(AND(ISNUMBER(SEARCH("CMT",$H185)),OR(ISNUMBER(SEARCH("완사입",$H185)),ISNUMBER(SEARCH("ODM",$H185)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H185)),"본사(소재팀)","생산처")))</f>
@@ -25250,10 +25093,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R186" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R186" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D186)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D186,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D186),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D186,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S186" s="25" t="n"/>
       <c r="T186" s="20">
@@ -25381,10 +25223,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R187" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R187" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D187)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D187,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D187),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D187,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S187" s="25" t="n"/>
       <c r="T187" s="20">
@@ -25508,10 +25349,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R188" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R188" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D188)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D188,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D188),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D188,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S188" s="25" t="n"/>
       <c r="T188" s="20">
@@ -25635,10 +25475,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R189" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R189" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D189)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D189,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D189),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D189,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S189" s="25" t="n"/>
       <c r="T189" s="20">
@@ -25762,10 +25601,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R190" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R190" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D190)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D190,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D190),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D190,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S190" s="25" t="n"/>
       <c r="T190" s="20">
@@ -25893,10 +25731,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R191" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R191" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D191)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D191,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D191),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D191,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S191" s="25" t="n"/>
       <c r="T191" s="20">
@@ -26024,10 +25861,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R192" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R192" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D192)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D192,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D192),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D192,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S192" s="25" t="n"/>
       <c r="T192" s="20">
@@ -26155,10 +25991,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R193" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R193" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D193)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D193,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D193),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D193,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S193" s="25" t="n"/>
       <c r="T193" s="20">
@@ -26290,10 +26125,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R194" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R194" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D194)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D194,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D194),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D194,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S194" s="25" t="n"/>
       <c r="T194" s="20">
@@ -26421,10 +26255,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R195" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R195" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D195)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D195,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D195),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D195,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S195" s="25" t="n"/>
       <c r="T195" s="20">
@@ -26552,10 +26385,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R196" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R196" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D196)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D196,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D196),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D196,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S196" s="25" t="n"/>
       <c r="T196" s="20">
@@ -26683,10 +26515,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R197" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R197" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D197)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D197,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D197),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D197,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S197" s="25" t="n"/>
       <c r="T197" s="20">
@@ -26814,10 +26645,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R198" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R198" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D198)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D198,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D198),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D198,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S198" s="25" t="n"/>
       <c r="T198" s="20">
@@ -26945,10 +26775,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R199" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R199" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D199)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D199,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D199),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D199,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S199" s="25" t="n"/>
       <c r="T199" s="20">
@@ -27076,10 +26905,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R200" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R200" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D200)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D200,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D200),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D200,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S200" s="25" t="n"/>
       <c r="T200" s="20">
@@ -27207,10 +27035,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R201" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R201" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D201)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D201,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D201),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D201,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S201" s="25" t="n"/>
       <c r="T201" s="20">
@@ -27338,10 +27165,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R202" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R202" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D202)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D202,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D202),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D202,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S202" s="25" t="n"/>
       <c r="T202" s="20">
@@ -27469,10 +27295,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R203" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R203" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D203)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D203,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D203),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D203,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S203" s="25" t="n"/>
       <c r="T203" s="20">
@@ -27596,10 +27421,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R204" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R204" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D204)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D204,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D204),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D204,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S204" s="25" t="n"/>
       <c r="T204" s="20">
@@ -27727,10 +27551,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R205" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R205" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D205)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D205,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D205),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D205,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S205" s="25" t="n"/>
       <c r="T205" s="20">
@@ -27858,10 +27681,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R206" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R206" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D206)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D206,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D206),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D206,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S206" s="25" t="n"/>
       <c r="T206" s="20">
@@ -27989,10 +27811,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R207" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R207" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D207)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D207,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D207),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D207,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S207" s="25" t="n"/>
       <c r="T207" s="20">
@@ -28124,10 +27945,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R208" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R208" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D208)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D208,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D208),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D208,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S208" s="25" t="n"/>
       <c r="T208" s="20">
@@ -28255,10 +28075,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R209" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R209" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D209)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D209,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D209),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D209,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S209" s="25" t="n"/>
       <c r="T209" s="20">
@@ -28386,10 +28205,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R210" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R210" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D210)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D210,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D210),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D210,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S210" s="25" t="n"/>
       <c r="T210" s="20">
@@ -28513,10 +28331,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R211" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R211" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D211)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D211,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D211),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D211,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S211" s="25" t="n"/>
       <c r="T211" s="20">
@@ -28648,10 +28465,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R212" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R212" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D212)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D212,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D212),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D212,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S212" s="25" t="n"/>
       <c r="T212" s="20">
@@ -28779,10 +28595,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R213" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R213" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D213)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D213,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D213),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D213,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S213" s="25" t="n"/>
       <c r="T213" s="20">
@@ -28910,10 +28725,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R214" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R214" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D214)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D214,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D214),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D214,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S214" s="25" t="n"/>
       <c r="T214" s="20">
@@ -29041,10 +28855,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R215" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R215" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D215)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D215,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D215),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D215,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S215" s="25" t="n"/>
       <c r="T215" s="20">
@@ -29168,10 +28981,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R216" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R216" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D216)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D216,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D216),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D216,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S216" s="25" t="n"/>
       <c r="T216" s="20">
@@ -29295,10 +29107,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R217" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R217" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D217)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D217,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D217),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D217,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S217" s="25" t="n"/>
       <c r="T217" s="20">
@@ -29422,10 +29233,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R218" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R218" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D218)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D218,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D218),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D218,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S218" s="25" t="n"/>
       <c r="T218" s="20">
@@ -29553,10 +29363,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R219" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R219" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D219)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D219,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D219),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D219,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S219" s="25" t="n"/>
       <c r="T219" s="20">
@@ -29684,10 +29493,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R220" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R220" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D220)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D220,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D220),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D220,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S220" s="25" t="n"/>
       <c r="T220" s="20">
@@ -29815,10 +29623,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R221" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R221" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D221)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D221,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D221),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D221,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S221" s="25" t="n"/>
       <c r="T221" s="20">
@@ -29946,10 +29753,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R222" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R222" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D222)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D222,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D222),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D222,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S222" s="25" t="n"/>
       <c r="T222" s="20">
@@ -30077,10 +29883,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R223" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R223" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D223)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D223,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D223),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D223,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S223" s="25" t="n"/>
       <c r="T223" s="20">
@@ -30208,10 +30013,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R224" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R224" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D224)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D224,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D224),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D224,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S224" s="25" t="n"/>
       <c r="T224" s="20">
@@ -30339,10 +30143,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R225" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R225" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D225)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D225,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D225),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D225,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S225" s="25" t="n"/>
       <c r="T225" s="20">
@@ -30470,10 +30273,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R226" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R226" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D226)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D226,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D226),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D226,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S226" s="25" t="n"/>
       <c r="T226" s="20">
@@ -30601,10 +30403,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R227" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R227" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D227)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D227,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D227),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D227,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S227" s="25" t="n"/>
       <c r="T227" s="20">
@@ -30736,10 +30537,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R228" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R228" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D228)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D228,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D228),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D228,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S228" s="25" t="n"/>
       <c r="T228" s="20">
@@ -30871,10 +30671,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R229" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R229" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D229)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D229,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D229),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D229,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S229" s="25" t="n"/>
       <c r="T229" s="20">
@@ -31006,10 +30805,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R230" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R230" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D230)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D230,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D230),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D230,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S230" s="25" t="n"/>
       <c r="T230" s="20">
@@ -31141,10 +30939,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R231" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R231" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D231)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D231,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D231),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D231,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S231" s="25" t="n"/>
       <c r="T231" s="20">
@@ -31276,10 +31073,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R232" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R232" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D232)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D232,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D232),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D232,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S232" s="25" t="n"/>
       <c r="T232" s="20">
@@ -31403,10 +31199,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R233" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R233" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D233)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D233,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D233),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D233,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S233" s="25" t="n"/>
       <c r="T233" s="20">
@@ -31530,10 +31325,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R234" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R234" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D234)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D234,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D234),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D234,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S234" s="25" t="n"/>
       <c r="T234" s="20">
@@ -31657,10 +31451,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R235" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R235" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D235)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D235,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D235),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D235,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S235" s="25" t="n"/>
       <c r="T235" s="20">
@@ -31788,10 +31581,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R236" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R236" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D236)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D236,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D236),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D236,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S236" s="25" t="n"/>
       <c r="T236" s="20">
@@ -31923,10 +31715,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R237" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R237" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D237)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D237,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D237),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D237,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S237" s="25" t="n"/>
       <c r="T237" s="20">
@@ -32054,10 +31845,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R238" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R238" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D238)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D238,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D238),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D238,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S238" s="25" t="n"/>
       <c r="T238" s="20">
@@ -32185,10 +31975,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R239" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R239" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D239)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D239,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D239),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D239,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S239" s="25" t="n"/>
       <c r="T239" s="20">
@@ -32316,10 +32105,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R240" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R240" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D240)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D240,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D240),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D240,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S240" s="25" t="n"/>
       <c r="T240" s="20">
@@ -32447,10 +32235,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R241" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R241" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D241)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D241,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D241),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D241,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S241" s="25" t="n"/>
       <c r="T241" s="20">
@@ -32578,10 +32365,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R242" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R242" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D242)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D242,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D242),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D242,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S242" s="25" t="n"/>
       <c r="T242" s="20">
@@ -32705,10 +32491,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R243" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R243" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D243)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D243,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D243),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D243,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S243" s="25" t="n"/>
       <c r="T243" s="20">
@@ -32832,7 +32617,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R244" s="21" t="n"/>
+      <c r="R244" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D244)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D244,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D244),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D244,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S244" s="25" t="n"/>
       <c r="T244" s="20">
         <f>IF($H244="","",IF(AND(ISNUMBER(SEARCH("CMT",$H244)),OR(ISNUMBER(SEARCH("완사입",$H244)),ISNUMBER(SEARCH("ODM",$H244)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H244)),"본사(소재팀)","생산처")))</f>
@@ -32947,10 +32735,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R245" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R245" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D245)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D245,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D245),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D245,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S245" s="25" t="n"/>
       <c r="T245" s="20">
@@ -33078,10 +32865,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R246" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R246" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D246)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D246,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D246),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D246,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S246" s="25" t="n"/>
       <c r="T246" s="20">
@@ -33209,7 +32995,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R247" s="21" t="n"/>
+      <c r="R247" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D247)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D247,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D247),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D247,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S247" s="25" t="n"/>
       <c r="T247" s="20">
         <f>IF($H247="","",IF(AND(ISNUMBER(SEARCH("CMT",$H247)),OR(ISNUMBER(SEARCH("완사입",$H247)),ISNUMBER(SEARCH("ODM",$H247)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H247)),"본사(소재팀)","생산처")))</f>
@@ -33324,7 +33113,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R248" s="21" t="n"/>
+      <c r="R248" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D248)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D248,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D248),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D248,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S248" s="25" t="n"/>
       <c r="T248" s="20">
         <f>IF($H248="","",IF(AND(ISNUMBER(SEARCH("CMT",$H248)),OR(ISNUMBER(SEARCH("완사입",$H248)),ISNUMBER(SEARCH("ODM",$H248)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H248)),"본사(소재팀)","생산처")))</f>
@@ -33439,10 +33231,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R249" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R249" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D249)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D249,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D249),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D249,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S249" s="25" t="n"/>
       <c r="T249" s="20">
@@ -33574,10 +33365,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R250" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R250" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D250)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D250,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D250),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D250,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S250" s="25" t="n"/>
       <c r="T250" s="20">
@@ -33705,10 +33495,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R251" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R251" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D251)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D251,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D251),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D251,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S251" s="25" t="n"/>
       <c r="T251" s="20">
@@ -33832,10 +33621,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R252" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R252" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D252)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D252,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D252),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D252,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S252" s="25" t="n"/>
       <c r="T252" s="20">
@@ -33963,10 +33751,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R253" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R253" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D253)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D253,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D253),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D253,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S253" s="25" t="n"/>
       <c r="T253" s="20">
@@ -34094,10 +33881,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R254" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R254" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D254)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D254,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D254),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D254,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S254" s="25" t="n"/>
       <c r="T254" s="20">
@@ -34221,10 +34007,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R255" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R255" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D255)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D255,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D255),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D255,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S255" s="25" t="n"/>
       <c r="T255" s="20">
@@ -34352,7 +34137,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R256" s="21" t="n"/>
+      <c r="R256" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D256)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D256,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D256),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D256,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S256" s="25" t="n"/>
       <c r="T256" s="20">
         <f>IF($H256="","",IF(AND(ISNUMBER(SEARCH("CMT",$H256)),OR(ISNUMBER(SEARCH("완사입",$H256)),ISNUMBER(SEARCH("ODM",$H256)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H256)),"본사(소재팀)","생산처")))</f>
@@ -34467,7 +34255,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R257" s="21" t="n"/>
+      <c r="R257" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D257)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D257,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D257),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D257,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S257" s="25" t="n"/>
       <c r="T257" s="20">
         <f>IF($H257="","",IF(AND(ISNUMBER(SEARCH("CMT",$H257)),OR(ISNUMBER(SEARCH("완사입",$H257)),ISNUMBER(SEARCH("ODM",$H257)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H257)),"본사(소재팀)","생산처")))</f>
@@ -34586,10 +34377,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R258" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R258" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D258)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D258,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D258),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D258,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S258" s="25" t="n"/>
       <c r="T258" s="20">
@@ -34713,10 +34503,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R259" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R259" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D259)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D259,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D259),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D259,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S259" s="25" t="n"/>
       <c r="T259" s="20">
@@ -34848,10 +34637,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R260" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R260" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D260)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D260,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D260),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D260,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S260" s="25" t="n"/>
       <c r="T260" s="20">
@@ -34983,10 +34771,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R261" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R261" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D261)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D261,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D261),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D261,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S261" s="25" t="n"/>
       <c r="T261" s="20">
@@ -35118,10 +34905,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R262" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R262" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D262)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D262,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D262),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D262,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S262" s="25" t="n"/>
       <c r="T262" s="20">
@@ -35249,10 +35035,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R263" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R263" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D263)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D263,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D263),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D263,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S263" s="25" t="n"/>
       <c r="T263" s="20">
@@ -35380,10 +35165,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R264" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R264" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D264)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D264,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D264),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D264,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S264" s="25" t="n"/>
       <c r="T264" s="20">
@@ -35511,10 +35295,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R265" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R265" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D265)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D265,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D265),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D265,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S265" s="25" t="n"/>
       <c r="T265" s="20">
@@ -35646,10 +35429,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R266" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R266" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D266)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D266,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D266),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D266,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S266" s="25" t="n"/>
       <c r="T266" s="20">
@@ -35777,10 +35559,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R267" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R267" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D267)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D267,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D267),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D267,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S267" s="25" t="n"/>
       <c r="T267" s="20">
@@ -35908,10 +35689,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R268" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R268" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D268)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D268,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D268),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D268,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S268" s="25" t="n"/>
       <c r="T268" s="20">
@@ -36043,10 +35823,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R269" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R269" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D269)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D269,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D269),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D269,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S269" s="25" t="n"/>
       <c r="T269" s="20">
@@ -36178,10 +35957,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R270" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R270" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D270)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D270,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D270),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D270,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S270" s="25" t="n"/>
       <c r="T270" s="20">
@@ -36309,10 +36087,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R271" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R271" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D271)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D271,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D271),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D271,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S271" s="25" t="n"/>
       <c r="T271" s="20">
@@ -36444,10 +36221,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R272" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R272" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D272)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D272,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D272),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D272,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S272" s="25" t="n"/>
       <c r="T272" s="20">
@@ -36579,10 +36355,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R273" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R273" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D273)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D273,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D273),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D273,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S273" s="25" t="n"/>
       <c r="T273" s="20">
@@ -36710,10 +36485,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R274" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R274" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D274)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D274,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D274),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D274,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S274" s="25" t="n"/>
       <c r="T274" s="20">
@@ -36841,10 +36615,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R275" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R275" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D275)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D275,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D275),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D275,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S275" s="25" t="n"/>
       <c r="T275" s="20">
@@ -36976,10 +36749,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R276" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R276" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D276)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D276,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D276),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D276,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S276" s="25" t="n"/>
       <c r="T276" s="20">
@@ -37111,10 +36883,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R277" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R277" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D277)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D277,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D277),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D277,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S277" s="25" t="n"/>
       <c r="T277" s="20">
@@ -37246,10 +37017,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R278" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R278" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D278)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D278,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D278),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D278,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S278" s="25" t="n"/>
       <c r="T278" s="20">
@@ -37381,10 +37151,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R279" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R279" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D279)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D279,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D279),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D279,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S279" s="25" t="n"/>
       <c r="T279" s="20">
@@ -37516,10 +37285,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R280" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R280" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D280)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D280,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D280),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D280,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S280" s="25" t="n"/>
       <c r="T280" s="20">
@@ -37651,10 +37419,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R281" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R281" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D281)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D281,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D281),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D281,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S281" s="25" t="n"/>
       <c r="T281" s="20">
@@ -37782,10 +37549,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R282" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R282" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D282)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D282,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D282),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D282,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S282" s="25" t="n"/>
       <c r="T282" s="20">
@@ -37917,10 +37683,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R283" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R283" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D283)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D283,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D283),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D283,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S283" s="25" t="n"/>
       <c r="T283" s="20">
@@ -38048,10 +37813,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R284" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R284" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D284)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D284,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D284),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D284,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S284" s="25" t="n"/>
       <c r="T284" s="20">
@@ -38179,10 +37943,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R285" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R285" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D285)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D285,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D285),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D285,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S285" s="25" t="n"/>
       <c r="T285" s="20">
@@ -38310,10 +38073,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R286" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R286" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D286)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D286,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D286),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D286,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S286" s="25" t="n"/>
       <c r="T286" s="20">
@@ -38441,10 +38203,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R287" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R287" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D287)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D287,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D287),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D287,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S287" s="25" t="n"/>
       <c r="T287" s="20">
@@ -38572,10 +38333,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R288" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R288" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D288)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D288,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D288),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D288,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S288" s="25" t="n"/>
       <c r="T288" s="20">
@@ -38703,10 +38463,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R289" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R289" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D289)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D289,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D289),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D289,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S289" s="25" t="n"/>
       <c r="T289" s="20">
@@ -38830,10 +38589,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R290" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R290" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D290)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D290,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D290),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D290,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S290" s="25" t="n"/>
       <c r="T290" s="20">
@@ -38957,10 +38715,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R291" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R291" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D291)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D291,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D291),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D291,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S291" s="25" t="n"/>
       <c r="T291" s="20">
@@ -39088,10 +38845,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R292" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R292" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D292)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D292,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D292),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D292,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S292" s="25" t="n"/>
       <c r="T292" s="20">
@@ -39223,10 +38979,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R293" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R293" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D293)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D293,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D293),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D293,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S293" s="25" t="n"/>
       <c r="T293" s="20">
@@ -39354,10 +39109,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R294" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R294" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D294)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D294,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D294),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D294,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S294" s="25" t="n"/>
       <c r="T294" s="20">
@@ -39481,10 +39235,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R295" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R295" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D295)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D295,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D295),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D295,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S295" s="25" t="n"/>
       <c r="T295" s="20">
@@ -39608,10 +39361,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R296" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R296" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D296)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D296,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D296),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D296,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S296" s="25" t="n"/>
       <c r="T296" s="20">
@@ -39735,10 +39487,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R297" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R297" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D297)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D297,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D297),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D297,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S297" s="25" t="n"/>
       <c r="T297" s="20">
@@ -39862,10 +39613,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R298" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R298" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D298)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D298,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D298),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D298,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S298" s="25" t="n"/>
       <c r="T298" s="20">
@@ -39989,10 +39739,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R299" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R299" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D299)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D299,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D299),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D299,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S299" s="25" t="n"/>
       <c r="T299" s="20">
@@ -40120,10 +39869,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R300" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R300" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D300)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D300,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D300),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D300,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S300" s="25" t="n"/>
       <c r="T300" s="20">
@@ -40251,10 +39999,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R301" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R301" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D301)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D301,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D301),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D301,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S301" s="25" t="n"/>
       <c r="T301" s="20">
@@ -40378,7 +40125,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R302" s="21" t="n"/>
+      <c r="R302" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D302)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D302,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D302),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D302,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S302" s="25" t="n"/>
       <c r="T302" s="20">
         <f>IF($H302="","",IF(AND(ISNUMBER(SEARCH("CMT",$H302)),OR(ISNUMBER(SEARCH("완사입",$H302)),ISNUMBER(SEARCH("ODM",$H302)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H302)),"본사(소재팀)","생산처")))</f>
@@ -40501,10 +40251,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R303" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R303" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D303)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D303,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D303),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D303,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S303" s="25" t="n"/>
       <c r="T303" s="20">
@@ -40628,7 +40377,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R304" s="21" t="n"/>
+      <c r="R304" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D304)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D304,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D304),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D304,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S304" s="25" t="n"/>
       <c r="T304" s="20">
         <f>IF($H304="","",IF(AND(ISNUMBER(SEARCH("CMT",$H304)),OR(ISNUMBER(SEARCH("완사입",$H304)),ISNUMBER(SEARCH("ODM",$H304)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H304)),"본사(소재팀)","생산처")))</f>
@@ -40755,10 +40507,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R305" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R305" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D305)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D305,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D305),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D305,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S305" s="25" t="n"/>
       <c r="T305" s="20">
@@ -40886,10 +40637,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R306" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R306" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D306)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D306,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D306),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D306,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S306" s="25" t="n"/>
       <c r="T306" s="20">
@@ -41017,7 +40767,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R307" s="21" t="n"/>
+      <c r="R307" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D307)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D307,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D307),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D307,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S307" s="25" t="n"/>
       <c r="T307" s="20">
         <f>IF($H307="","",IF(AND(ISNUMBER(SEARCH("CMT",$H307)),OR(ISNUMBER(SEARCH("완사입",$H307)),ISNUMBER(SEARCH("ODM",$H307)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H307)),"본사(소재팀)","생산처")))</f>
@@ -41140,10 +40893,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R308" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R308" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D308)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D308,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D308),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D308,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S308" s="25" t="n"/>
       <c r="T308" s="20">
@@ -41275,10 +41027,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R309" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R309" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D309)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D309,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D309),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D309,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S309" s="25" t="n"/>
       <c r="T309" s="20">
@@ -41402,10 +41153,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R310" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R310" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D310)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D310,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D310),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D310,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S310" s="25" t="n"/>
       <c r="T310" s="20">
@@ -41533,10 +41283,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R311" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R311" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D311)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D311,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D311),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D311,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S311" s="25" t="n"/>
       <c r="T311" s="20">
@@ -41668,7 +41417,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R312" s="21" t="n"/>
+      <c r="R312" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D312)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D312,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D312),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D312,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S312" s="25" t="n"/>
       <c r="T312" s="20">
         <f>IF($H312="","",IF(AND(ISNUMBER(SEARCH("CMT",$H312)),OR(ISNUMBER(SEARCH("완사입",$H312)),ISNUMBER(SEARCH("ODM",$H312)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H312)),"본사(소재팀)","생산처")))</f>
@@ -41791,10 +41543,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R313" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R313" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D313)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D313,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D313),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D313,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S313" s="25" t="n"/>
       <c r="T313" s="20">
@@ -41922,10 +41673,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R314" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R314" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D314)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D314,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D314),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D314,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S314" s="25" t="n"/>
       <c r="T314" s="20">
@@ -42057,10 +41807,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R315" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R315" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D315)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D315,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D315),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D315,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S315" s="25" t="n"/>
       <c r="T315" s="20">
@@ -42192,10 +41941,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R316" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R316" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D316)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D316,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D316),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D316,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S316" s="25" t="n"/>
       <c r="T316" s="20">
@@ -42327,10 +42075,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R317" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R317" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D317)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D317,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D317),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D317,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S317" s="25" t="n"/>
       <c r="T317" s="20">
@@ -42458,10 +42205,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R318" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R318" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D318)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D318,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D318),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D318,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S318" s="25" t="n"/>
       <c r="T318" s="20">
@@ -42589,10 +42335,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R319" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R319" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D319)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D319,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D319),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D319,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S319" s="25" t="n"/>
       <c r="T319" s="20">
@@ -42720,10 +42465,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R320" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R320" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D320)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D320,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D320),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D320,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S320" s="25" t="n"/>
       <c r="T320" s="20">
@@ -42851,10 +42595,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R321" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R321" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D321)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D321,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D321),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D321,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S321" s="25" t="n"/>
       <c r="T321" s="20">
@@ -42982,10 +42725,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R322" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R322" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D322)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D322,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D322),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D322,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S322" s="25" t="n"/>
       <c r="T322" s="20">
@@ -43113,10 +42855,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R323" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R323" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D323)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D323,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D323),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D323,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S323" s="25" t="n"/>
       <c r="T323" s="20">
@@ -43244,10 +42985,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R324" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R324" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D324)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D324,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D324),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D324,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S324" s="25" t="n"/>
       <c r="T324" s="20">
@@ -43375,10 +43115,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R325" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R325" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D325)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D325,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D325),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D325,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S325" s="25" t="n"/>
       <c r="T325" s="20">
@@ -43506,10 +43245,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R326" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R326" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D326)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D326,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D326),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D326,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S326" s="25" t="n"/>
       <c r="T326" s="20">
@@ -43637,10 +43375,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R327" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R327" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D327)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D327,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D327),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D327,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S327" s="25" t="n"/>
       <c r="T327" s="20">
@@ -43768,10 +43505,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R328" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R328" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D328)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D328,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D328),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D328,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S328" s="25" t="n"/>
       <c r="T328" s="20">
@@ -43899,10 +43635,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R329" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R329" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D329)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D329,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D329),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D329,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S329" s="25" t="n"/>
       <c r="T329" s="20">
@@ -44030,10 +43765,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R330" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R330" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D330)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D330,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D330),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D330,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S330" s="25" t="n"/>
       <c r="T330" s="20">
@@ -44161,10 +43895,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R331" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R331" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D331)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D331,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D331),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D331,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S331" s="25" t="n"/>
       <c r="T331" s="20">
@@ -44292,10 +44025,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R332" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R332" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D332)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D332,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D332),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D332,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S332" s="25" t="n"/>
       <c r="T332" s="20">
@@ -44423,10 +44155,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R333" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R333" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D333)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D333,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D333),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D333,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S333" s="25" t="n"/>
       <c r="T333" s="20">
@@ -44554,10 +44285,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R334" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R334" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D334)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D334,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D334),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D334,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S334" s="25" t="n"/>
       <c r="T334" s="20">
@@ -44685,10 +44415,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R335" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R335" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D335)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D335,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D335),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D335,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S335" s="25" t="n"/>
       <c r="T335" s="20">
@@ -44816,10 +44545,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R336" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R336" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D336)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D336,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D336),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D336,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S336" s="25" t="n"/>
       <c r="T336" s="20">
@@ -44947,10 +44675,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R337" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R337" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D337)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D337,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D337),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D337,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S337" s="25" t="n"/>
       <c r="T337" s="20">
@@ -45078,10 +44805,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R338" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R338" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D338)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D338,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D338),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D338,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S338" s="25" t="n"/>
       <c r="T338" s="20">
@@ -45209,10 +44935,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R339" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R339" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D339)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D339,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D339),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D339,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S339" s="25" t="n"/>
       <c r="T339" s="20">
@@ -45340,10 +45065,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R340" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R340" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D340)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D340,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D340),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D340,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S340" s="25" t="n"/>
       <c r="T340" s="20">
@@ -45467,7 +45191,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R341" s="21" t="n"/>
+      <c r="R341" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D341)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D341,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D341),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D341,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S341" s="25" t="n"/>
       <c r="T341" s="20">
         <f>IF($H341="","",IF(AND(ISNUMBER(SEARCH("CMT",$H341)),OR(ISNUMBER(SEARCH("완사입",$H341)),ISNUMBER(SEARCH("ODM",$H341)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H341)),"본사(소재팀)","생산처")))</f>
@@ -45582,7 +45309,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R342" s="21" t="n"/>
+      <c r="R342" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D342)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D342,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D342),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D342,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S342" s="25" t="n"/>
       <c r="T342" s="20">
         <f>IF($H342="","",IF(AND(ISNUMBER(SEARCH("CMT",$H342)),OR(ISNUMBER(SEARCH("완사입",$H342)),ISNUMBER(SEARCH("ODM",$H342)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H342)),"본사(소재팀)","생산처")))</f>
@@ -45697,7 +45427,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R343" s="21" t="n"/>
+      <c r="R343" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D343)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D343,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D343),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D343,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S343" s="25" t="n"/>
       <c r="T343" s="20">
         <f>IF($H343="","",IF(AND(ISNUMBER(SEARCH("CMT",$H343)),OR(ISNUMBER(SEARCH("완사입",$H343)),ISNUMBER(SEARCH("ODM",$H343)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H343)),"본사(소재팀)","생산처")))</f>
@@ -45816,10 +45549,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R344" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R344" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D344)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D344,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D344),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D344,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S344" s="25" t="n"/>
       <c r="T344" s="20">
@@ -45951,10 +45683,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R345" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R345" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D345)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D345,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D345),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D345,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S345" s="25" t="n"/>
       <c r="T345" s="20">
@@ -46086,10 +45817,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R346" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R346" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D346)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D346,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D346),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D346,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S346" s="25" t="n"/>
       <c r="T346" s="20">
@@ -46217,10 +45947,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R347" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R347" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D347)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D347,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D347),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D347,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S347" s="25" t="n"/>
       <c r="T347" s="20">
@@ -46348,10 +46077,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R348" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R348" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D348)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D348,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D348),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D348,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S348" s="25" t="n"/>
       <c r="T348" s="20">
@@ -46479,10 +46207,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R349" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R349" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D349)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D349,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D349),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D349,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S349" s="25" t="n"/>
       <c r="T349" s="20">
@@ -46610,10 +46337,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R350" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R350" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D350)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D350,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D350),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D350,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S350" s="25" t="n"/>
       <c r="T350" s="20">
@@ -46741,10 +46467,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R351" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R351" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D351)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D351,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D351),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D351,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S351" s="25" t="n"/>
       <c r="T351" s="20">
@@ -46872,10 +46597,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R352" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R352" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D352)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D352,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D352),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D352,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S352" s="25" t="n"/>
       <c r="T352" s="20">
@@ -47003,10 +46727,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R353" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R353" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D353)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D353,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D353),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D353,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S353" s="25" t="n"/>
       <c r="T353" s="20">
@@ -47134,10 +46857,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R354" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R354" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D354)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D354,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D354),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D354,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S354" s="25" t="n"/>
       <c r="T354" s="20">
@@ -47265,10 +46987,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R355" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R355" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D355)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D355,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D355),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D355,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S355" s="25" t="n"/>
       <c r="T355" s="20">
@@ -47396,10 +47117,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R356" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R356" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D356)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D356,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D356),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D356,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S356" s="25" t="n"/>
       <c r="T356" s="20">
@@ -47531,10 +47251,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R357" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R357" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D357)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D357,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D357),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D357,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S357" s="25" t="n"/>
       <c r="T357" s="20">
@@ -47662,7 +47381,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R358" s="21" t="n"/>
+      <c r="R358" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D358)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D358,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D358),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D358,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S358" s="25" t="n"/>
       <c r="T358" s="20">
         <f>IF($H358="","",IF(AND(ISNUMBER(SEARCH("CMT",$H358)),OR(ISNUMBER(SEARCH("완사입",$H358)),ISNUMBER(SEARCH("ODM",$H358)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H358)),"본사(소재팀)","생산처")))</f>
@@ -47789,10 +47511,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R359" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R359" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D359)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D359,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D359),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D359,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S359" s="25" t="n"/>
       <c r="T359" s="20">
@@ -47920,10 +47641,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R360" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R360" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D360)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D360,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D360),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D360,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S360" s="25" t="n"/>
       <c r="T360" s="20">
@@ -48051,10 +47771,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R361" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R361" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D361)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D361,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D361),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D361,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S361" s="25" t="n"/>
       <c r="T361" s="20">
@@ -48182,10 +47901,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R362" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R362" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D362)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D362,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D362),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D362,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S362" s="25" t="n"/>
       <c r="T362" s="20">
@@ -48313,10 +48031,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R363" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R363" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D363)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D363,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D363),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D363,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S363" s="25" t="n"/>
       <c r="T363" s="20">
@@ -48444,10 +48161,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R364" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R364" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D364)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D364,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D364),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D364,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S364" s="25" t="n"/>
       <c r="T364" s="20">
@@ -48575,10 +48291,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R365" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R365" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D365)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D365,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D365),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D365,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S365" s="25" t="n"/>
       <c r="T365" s="20">
@@ -48706,10 +48421,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R366" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R366" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D366)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D366,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D366),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D366,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S366" s="25" t="n"/>
       <c r="T366" s="20">
@@ -48833,10 +48547,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R367" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R367" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D367)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D367,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D367),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D367,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S367" s="25" t="n"/>
       <c r="T367" s="20">
@@ -48960,10 +48673,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R368" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R368" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D368)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D368,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D368),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D368,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S368" s="25" t="n"/>
       <c r="T368" s="20">
@@ -49087,10 +48799,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R369" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R369" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D369)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D369,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D369),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D369,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S369" s="25" t="n"/>
       <c r="T369" s="20">
@@ -49214,10 +48925,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R370" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R370" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D370)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D370,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D370),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D370,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S370" s="25" t="n"/>
       <c r="T370" s="20">
@@ -49341,7 +49051,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R371" s="21" t="n"/>
+      <c r="R371" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D371)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D371,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D371),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D371,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S371" s="25" t="n"/>
       <c r="T371" s="20">
         <f>IF($H371="","",IF(AND(ISNUMBER(SEARCH("CMT",$H371)),OR(ISNUMBER(SEARCH("완사입",$H371)),ISNUMBER(SEARCH("ODM",$H371)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H371)),"본사(소재팀)","생산처")))</f>
@@ -49464,10 +49177,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R372" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R372" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D372)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D372,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D372),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D372,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S372" s="25" t="n"/>
       <c r="T372" s="20">
@@ -49591,10 +49303,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R373" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R373" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D373)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D373,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D373),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D373,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S373" s="25" t="n"/>
       <c r="T373" s="20">
@@ -49718,10 +49429,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R374" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R374" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D374)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D374,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D374),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D374,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S374" s="25" t="n"/>
       <c r="T374" s="20">
@@ -49845,10 +49555,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R375" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R375" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D375)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D375,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D375),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D375,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S375" s="25" t="n"/>
       <c r="T375" s="20">
@@ -49972,10 +49681,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R376" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R376" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D376)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D376,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D376),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D376,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S376" s="25" t="n"/>
       <c r="T376" s="20">
@@ -50103,10 +49811,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R377" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R377" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D377)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D377,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D377),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D377,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S377" s="25" t="n"/>
       <c r="T377" s="20">
@@ -50234,10 +49941,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R378" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R378" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D378)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D378,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D378),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D378,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S378" s="25" t="n"/>
       <c r="T378" s="20">
@@ -50365,10 +50071,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R379" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R379" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D379)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D379,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D379),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D379,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S379" s="25" t="n"/>
       <c r="T379" s="20">
@@ -50496,10 +50201,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R380" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R380" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D380)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D380,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D380),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D380,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S380" s="25" t="n"/>
       <c r="T380" s="20">
@@ -50623,10 +50327,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R381" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R381" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D381)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D381,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D381),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D381,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S381" s="25" t="n"/>
       <c r="T381" s="20">
@@ -50754,10 +50457,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R382" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R382" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D382)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D382,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D382),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D382,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S382" s="25" t="n"/>
       <c r="T382" s="20">
@@ -50885,10 +50587,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R383" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R383" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D383)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D383,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D383),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D383,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S383" s="25" t="n"/>
       <c r="T383" s="20">
@@ -51012,10 +50713,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R384" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R384" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D384)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D384,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D384),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D384,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S384" s="25" t="n"/>
       <c r="T384" s="20">
@@ -51139,10 +50839,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R385" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R385" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D385)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D385,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D385),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D385,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S385" s="25" t="n"/>
       <c r="T385" s="20">
@@ -51270,10 +50969,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R386" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R386" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D386)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D386,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D386),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D386,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S386" s="25" t="n"/>
       <c r="T386" s="20">
@@ -51401,10 +51099,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R387" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R387" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D387)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D387,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D387),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D387,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S387" s="25" t="n"/>
       <c r="T387" s="20">
@@ -51536,10 +51233,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R388" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R388" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D388)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D388,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D388),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D388,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S388" s="25" t="n"/>
       <c r="T388" s="20">
@@ -51671,10 +51367,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R389" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R389" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D389)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D389,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D389),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D389,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S389" s="25" t="n"/>
       <c r="T389" s="20">
@@ -51806,10 +51501,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R390" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R390" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D390)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D390,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D390),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D390,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S390" s="25" t="n"/>
       <c r="T390" s="20">
@@ -51941,10 +51635,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R391" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R391" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D391)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D391,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D391),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D391,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S391" s="25" t="n"/>
       <c r="T391" s="20">
@@ -52076,10 +51769,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R392" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R392" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D392)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D392,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D392),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D392,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S392" s="25" t="n"/>
       <c r="T392" s="20">
@@ -52207,10 +51899,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R393" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R393" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D393)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D393,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D393),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D393,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S393" s="25" t="n"/>
       <c r="T393" s="20">
@@ -52338,7 +52029,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R394" s="21" t="n"/>
+      <c r="R394" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D394)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D394,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D394),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D394,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S394" s="25" t="n"/>
       <c r="T394" s="20">
         <f>IF($H394="","",IF(AND(ISNUMBER(SEARCH("CMT",$H394)),OR(ISNUMBER(SEARCH("완사입",$H394)),ISNUMBER(SEARCH("ODM",$H394)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H394)),"본사(소재팀)","생산처")))</f>
@@ -52461,10 +52155,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R395" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R395" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D395)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D395,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D395),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D395,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S395" s="25" t="n"/>
       <c r="T395" s="20">
@@ -52588,7 +52281,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R396" s="21" t="n"/>
+      <c r="R396" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D396)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D396,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D396),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D396,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S396" s="25" t="n"/>
       <c r="T396" s="20">
         <f>IF($H396="","",IF(AND(ISNUMBER(SEARCH("CMT",$H396)),OR(ISNUMBER(SEARCH("완사입",$H396)),ISNUMBER(SEARCH("ODM",$H396)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H396)),"본사(소재팀)","생산처")))</f>
@@ -52707,7 +52403,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R397" s="21" t="n"/>
+      <c r="R397" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D397)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D397,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D397),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D397,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S397" s="25" t="n"/>
       <c r="T397" s="20">
         <f>IF($H397="","",IF(AND(ISNUMBER(SEARCH("CMT",$H397)),OR(ISNUMBER(SEARCH("완사입",$H397)),ISNUMBER(SEARCH("ODM",$H397)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H397)),"본사(소재팀)","생산처")))</f>
@@ -52818,7 +52517,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R398" s="21" t="n"/>
+      <c r="R398" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D398)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D398,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D398),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D398,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S398" s="25" t="n"/>
       <c r="T398" s="20">
         <f>IF($H398="","",IF(AND(ISNUMBER(SEARCH("CMT",$H398)),OR(ISNUMBER(SEARCH("완사입",$H398)),ISNUMBER(SEARCH("ODM",$H398)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H398)),"본사(소재팀)","생산처")))</f>
@@ -52929,7 +52631,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R399" s="21" t="n"/>
+      <c r="R399" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D399)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D399,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D399),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D399,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S399" s="25" t="n"/>
       <c r="T399" s="20">
         <f>IF($H399="","",IF(AND(ISNUMBER(SEARCH("CMT",$H399)),OR(ISNUMBER(SEARCH("완사입",$H399)),ISNUMBER(SEARCH("ODM",$H399)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H399)),"본사(소재팀)","생산처")))</f>
@@ -53040,7 +52745,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R400" s="21" t="n"/>
+      <c r="R400" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D400)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D400,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D400),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D400,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S400" s="25" t="n"/>
       <c r="T400" s="20">
         <f>IF($H400="","",IF(AND(ISNUMBER(SEARCH("CMT",$H400)),OR(ISNUMBER(SEARCH("완사입",$H400)),ISNUMBER(SEARCH("ODM",$H400)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H400)),"본사(소재팀)","생산처")))</f>
@@ -53151,7 +52859,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R401" s="21" t="n"/>
+      <c r="R401" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D401)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D401,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D401),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D401,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S401" s="25" t="n"/>
       <c r="T401" s="20">
         <f>IF($H401="","",IF(AND(ISNUMBER(SEARCH("CMT",$H401)),OR(ISNUMBER(SEARCH("완사입",$H401)),ISNUMBER(SEARCH("ODM",$H401)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H401)),"본사(소재팀)","생산처")))</f>
@@ -53262,7 +52973,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R402" s="21" t="n"/>
+      <c r="R402" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D402)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D402,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D402),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D402,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S402" s="25" t="n"/>
       <c r="T402" s="20">
         <f>IF($H402="","",IF(AND(ISNUMBER(SEARCH("CMT",$H402)),OR(ISNUMBER(SEARCH("완사입",$H402)),ISNUMBER(SEARCH("ODM",$H402)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H402)),"본사(소재팀)","생산처")))</f>
@@ -53373,7 +53087,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R403" s="21" t="n"/>
+      <c r="R403" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D403)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D403,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D403),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D403,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S403" s="25" t="n"/>
       <c r="T403" s="20">
         <f>IF($H403="","",IF(AND(ISNUMBER(SEARCH("CMT",$H403)),OR(ISNUMBER(SEARCH("완사입",$H403)),ISNUMBER(SEARCH("ODM",$H403)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H403)),"본사(소재팀)","생산처")))</f>
@@ -53484,7 +53201,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R404" s="21" t="n"/>
+      <c r="R404" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D404)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D404,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D404),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D404,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S404" s="25" t="n"/>
       <c r="T404" s="20">
         <f>IF($H404="","",IF(AND(ISNUMBER(SEARCH("CMT",$H404)),OR(ISNUMBER(SEARCH("완사입",$H404)),ISNUMBER(SEARCH("ODM",$H404)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H404)),"본사(소재팀)","생산처")))</f>
@@ -53595,7 +53315,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R405" s="21" t="n"/>
+      <c r="R405" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D405)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D405,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D405),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D405,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S405" s="25" t="n"/>
       <c r="T405" s="20">
         <f>IF($H405="","",IF(AND(ISNUMBER(SEARCH("CMT",$H405)),OR(ISNUMBER(SEARCH("완사입",$H405)),ISNUMBER(SEARCH("ODM",$H405)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H405)),"본사(소재팀)","생산처")))</f>
@@ -53706,7 +53429,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R406" s="21" t="n"/>
+      <c r="R406" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D406)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D406,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D406),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D406,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S406" s="25" t="n"/>
       <c r="T406" s="20">
         <f>IF($H406="","",IF(AND(ISNUMBER(SEARCH("CMT",$H406)),OR(ISNUMBER(SEARCH("완사입",$H406)),ISNUMBER(SEARCH("ODM",$H406)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H406)),"본사(소재팀)","생산처")))</f>
@@ -53821,10 +53547,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R407" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R407" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D407)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D407,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D407),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D407,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S407" s="25" t="n"/>
       <c r="T407" s="20">
@@ -53948,10 +53673,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R408" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R408" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D408)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D408,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D408),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D408,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S408" s="25" t="n"/>
       <c r="T408" s="20">
@@ -54075,10 +53799,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R409" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R409" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D409)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D409,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D409),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D409,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S409" s="25" t="n"/>
       <c r="T409" s="20">
@@ -54202,10 +53925,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R410" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R410" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D410)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D410,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D410),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D410,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S410" s="25" t="n"/>
       <c r="T410" s="20">
@@ -54329,10 +54051,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R411" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R411" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D411)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D411,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D411),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D411,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S411" s="25" t="n"/>
       <c r="T411" s="20">
@@ -54456,10 +54177,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R412" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R412" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D412)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D412,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D412),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D412,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S412" s="25" t="n"/>
       <c r="T412" s="20">
@@ -54583,10 +54303,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R413" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R413" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D413)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D413,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D413),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D413,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S413" s="25" t="n"/>
       <c r="T413" s="20">
@@ -54710,10 +54429,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R414" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R414" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D414)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D414,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D414),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D414,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S414" s="25" t="n"/>
       <c r="T414" s="20">
@@ -54837,10 +54555,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R415" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R415" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D415)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D415,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D415),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D415,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S415" s="25" t="n"/>
       <c r="T415" s="20">
@@ -54968,10 +54685,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R416" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R416" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D416)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D416,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D416),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D416,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S416" s="25" t="n"/>
       <c r="T416" s="20">
@@ -55103,10 +54819,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R417" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R417" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D417)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D417,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D417),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D417,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S417" s="25" t="n"/>
       <c r="T417" s="20">
@@ -55234,7 +54949,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R418" s="21" t="n"/>
+      <c r="R418" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D418)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D418,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D418),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D418,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
+      </c>
       <c r="S418" s="25" t="n"/>
       <c r="T418" s="20">
         <f>IF($H418="","",IF(AND(ISNUMBER(SEARCH("CMT",$H418)),OR(ISNUMBER(SEARCH("완사입",$H418)),ISNUMBER(SEARCH("ODM",$H418)))),"본사/생산처 혼재",IF(ISNUMBER(SEARCH("CMT",$H418)),"본사(소재팀)","생산처")))</f>
@@ -55361,10 +55079,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R419" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R419" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D419)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D419,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D419),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D419,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S419" s="25" t="n"/>
       <c r="T419" s="20">
@@ -55492,10 +55209,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R420" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R420" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D420)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D420,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D420),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D420,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S420" s="25" t="n"/>
       <c r="T420" s="20">
@@ -55623,10 +55339,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R421" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R421" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D421)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D421,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D421),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D421,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S421" s="25" t="n"/>
       <c r="T421" s="20">
@@ -55754,10 +55469,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R422" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R422" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D422)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D422,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D422),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D422,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S422" s="25" t="n"/>
       <c r="T422" s="20">
@@ -55885,10 +55599,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R423" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R423" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D423)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D423,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D423),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D423,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S423" s="25" t="n"/>
       <c r="T423" s="20">
@@ -56012,10 +55725,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R424" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R424" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D424)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D424,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D424),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D424,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S424" s="25" t="n"/>
       <c r="T424" s="20">
@@ -56143,10 +55855,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R425" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R425" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D425)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D425,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D425),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D425,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S425" s="25" t="n"/>
       <c r="T425" s="20">
@@ -56270,10 +55981,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R426" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R426" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D426)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D426,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D426),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D426,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S426" s="25" t="n"/>
       <c r="T426" s="20">
@@ -56397,10 +56107,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R427" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="R427" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D427)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D427,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D427),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D427,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S427" s="25" t="n"/>
       <c r="T427" s="20">
@@ -56528,10 +56237,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R428" s="21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
+      <c r="R428" s="19">
+        <f>IF(COUNTIF(EDW_RAW!$A$2:$A$1500,$D428)=0,"",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D428,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")=COUNTIF(EDW_RAW!$A$2:$A$1500,$D428),"O",IF(COUNTIFS(EDW_RAW!$A$2:$A$1500,$D428,EDW_RAW!$U$2:$U$1500,"&lt;&gt;~",EDW_RAW!$U$2:$U$1500,"&lt;&gt;")&gt;0,"부분","X")))</f>
+        <v/>
       </c>
       <c r="S428" s="25" t="n"/>
       <c r="T428" s="20">
@@ -56611,14 +56319,11 @@
       <formula>NOT(ISERROR(SEARCH("O",P5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="P5:P428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
     <dataValidation sqref="Q5:Q428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,부분,X"</formula1>
-    </dataValidation>
-    <dataValidation sqref="R5:R428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"O,부분,X"</formula1>
     </dataValidation>
     <dataValidation sqref="AG5:AG428" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -56662,6 +56367,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>'27SS 생산 프로세스 진척현황(자동화)' &gt; EDW_RAW 실시간 연동. 최초 1회 A2 셀에서 '액세스 허용' 클릭 필요. 이 탭은 수정하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>IMPORTRANGE("https://docs.google.com/spreadsheets/d/1iSDzZFUv3855k9Zh-tNZALH8z3gY7dTw9j8RlHpJETg","EDW_RAW!A2:U1500")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -56949,7 +56681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
